--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.39933301704593</v>
+        <v>2.989891615269963</v>
       </c>
       <c r="D2" t="n">
-        <v>18.46036388918848</v>
+        <v>2.999809131993128</v>
       </c>
       <c r="E2" t="n">
-        <v>10.74171758822446</v>
+        <v>1.745529108086475</v>
       </c>
       <c r="F2" t="n">
-        <v>28.79614502029959</v>
+        <v>4.679373565798684</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.28000925294685</v>
+        <v>5.570501503603863</v>
       </c>
       <c r="D3" t="n">
-        <v>34.3711004474544</v>
+        <v>5.585303822711341</v>
       </c>
       <c r="E3" t="n">
-        <v>10.74171758822446</v>
+        <v>1.745529108086475</v>
       </c>
       <c r="F3" t="n">
-        <v>28.79614502029959</v>
+        <v>4.679373565798684</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.50786661696809</v>
+        <v>7.232528325257316</v>
       </c>
       <c r="D4" t="n">
-        <v>85.92722015816805</v>
+        <v>13.96317327570231</v>
       </c>
       <c r="E4" t="n">
-        <v>10.74171758822446</v>
+        <v>1.745529108086475</v>
       </c>
       <c r="F4" t="n">
-        <v>28.79614502029959</v>
+        <v>4.679373565798684</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
